--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>60</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>22/08 18:45</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>55</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>30/08 23:00</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>60</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>60</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>24/08 18:30</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>60</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>55</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>55</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>24/08 14:30</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>55</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>1.72</t>
-        </is>
+      <c r="F10" t="n">
+        <v>1.72</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>25/08 20:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>55</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>50</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>50</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>24/08 23:00</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>55</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>23/08 15:45</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>55</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>25/08 22:00</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>50</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>24/08 21:30</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>55</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>23/08 19:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F18" t="n">
+        <v>2.5</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>24/08 19:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>55</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>24/08 12:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>60</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>24/08 15:00</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>50</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>23/08 18:30</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>50</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>31/08 01:00</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>50</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>25/08 14:30</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F24" t="n">
+        <v>2.85</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>50</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
       </c>
     </row>
     <row r="26">
@@ -1585,10 +1537,8 @@
           <t>24/08 17:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F26" t="n">
+        <v>55</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1601,7 +1551,52 @@
         </is>
       </c>
       <c r="I26" s="2" t="n">
-        <v>45890.07175645651</v>
+        <v>45890.07175645833</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball | X(12:0)P | Monténégro</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PMU(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Monténégro – AllemagneBasket FIBA. EuroBasket</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>X(12:0)P</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>27/08 13:30</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>19.75</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+7,08%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45890.13151873703</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -1580,10 +1580,8 @@
           <t>27/08 13:30</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>19.75</t>
-        </is>
+      <c r="F27" t="n">
+        <v>19.75</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45890.13151873703</v>
+        <v>45890.13151873842</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,6 +1597,141 @@
         <v>45890.13151873842</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball | X2e période[race to 15 regular time] | Washington</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PokerStars(FR)Basketball</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Washington Mystics – Connecticut SunUSA - WNBA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>X2e période[race to 15 regular time]</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>21/08 23:00</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+13,3%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45890.22345772882</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 1 / DNB | AE Realida</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AE Realidade Jovem SP – Corinthians (W)Brazil - Paulista (W)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1 / DNB</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>32.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3,39%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+8,45%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45890.22345772882</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 21-2- se qualifie | River Plat</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>River Plate (ARG) – Libertad AsuncionInternational. Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>22/08 00:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>16,4%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+6,67%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45890.22345772882</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1623,10 +1623,8 @@
           <t>21/08 23:00</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>20.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>20</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1639,7 +1637,7 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45890.22345772882</v>
+        <v>45890.22345773148</v>
       </c>
     </row>
     <row r="29">
@@ -1668,10 +1666,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>32.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>32</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1684,7 +1680,7 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45890.22345772882</v>
+        <v>45890.22345773148</v>
       </c>
     </row>
     <row r="30">
@@ -1713,10 +1709,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="F30" t="n">
+        <v>6.5</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1729,7 +1723,367 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45890.22345772882</v>
+        <v>45890.22345773148</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 24.5 - tirs | Heidenheim</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Heidenheim – WolfsburgAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>23/08 13:30</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>44,6%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+24,8%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45890.27920796935</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 11.5 - tirs1re équipe | Burnley – </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Burnley – SunderlandAngleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Moins que 11.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>23/08 14:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>45,6%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+18,7%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45890.27920796935</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 26.5 - tirs | Manchester</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Manchester City – TottenhamAngleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Moins que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>23/08 11:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+17,1%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45890.27920796935</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 29.5 - tirs | Bayern Mun</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Bayern Munich – RB LeipzigAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Moins que 29.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>63,2%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+13,8%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45890.27920796935</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs1re équipe | Anderlecht</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Anderlecht – AEK AthènesEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+12,9%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45890.27920796935</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Majorque –</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Majorque – Celta VigoEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>23/08 15:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>50,1%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+12,8%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45890.27920796935</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 5.5 | CA Indepen</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CA Independiente – CA PlatenseLiga Profesional</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Plus que 5.5</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>24/08 23:30</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+11,0%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45890.27920796935</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 21-2- se qualifie | Santa Clar</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Santa Clara – Shamrock RoversEurope - Ligue  Conférence (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>21-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>27,3%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+9,12%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45890.27920796935</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,10 +1752,8 @@
           <t>23/08 13:30</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F31" t="n">
+        <v>2.8</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1768,7 +1766,7 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
       </c>
     </row>
     <row r="32">
@@ -1797,10 +1795,8 @@
           <t>23/08 14:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
+      <c r="F32" t="n">
+        <v>2.6</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1813,7 +1809,7 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
       </c>
     </row>
     <row r="33">
@@ -1842,10 +1838,8 @@
           <t>23/08 11:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F33" t="n">
+        <v>2.8</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1858,7 +1852,7 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
       </c>
     </row>
     <row r="34">
@@ -1887,10 +1881,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
+      <c r="F34" t="n">
+        <v>1.8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1903,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
       </c>
     </row>
     <row r="35">
@@ -1932,10 +1924,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
+      <c r="F35" t="n">
+        <v>2.8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1948,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
       </c>
     </row>
     <row r="36">
@@ -1977,10 +1967,8 @@
           <t>23/08 15:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="F36" t="n">
+        <v>2.25</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1993,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
       </c>
     </row>
     <row r="37">
@@ -2022,10 +2010,8 @@
           <t>24/08 23:30</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F37" t="n">
+        <v>50</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -2038,7 +2024,7 @@
         </is>
       </c>
       <c r="I37" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
       </c>
     </row>
     <row r="38">
@@ -2067,10 +2053,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="F38" t="n">
+        <v>4</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -2083,7 +2067,187 @@
         </is>
       </c>
       <c r="I38" s="2" t="n">
-        <v>45890.27920796935</v>
+        <v>45890.27920797453</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | Atletico L</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Atletico Lanus – Central CórdobaInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>22/08 00:30</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>30,6%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+37,7%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45890.30793214786</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 17.5 - tirs2e équipe | Levante – </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Levante – BarceloneEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Moins que 17.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>23/08 19:30</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>2.95</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+18,9%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45890.30793214786</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 16.5 - tirs1re équipe | Atlético M</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Atlético Madrid – ElcheEspagne - Espagne LaLiga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Moins que 16.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>23/08 17:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>39,7%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+13,1%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45890.30793214786</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 9.5 - tirs1re équipe | Brentford </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Brentford – Aston VillaAngleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>23/08 14:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>37,7%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+9,36%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45890.30793214786</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2096,10 +2096,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F39" t="n">
+        <v>4.5</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45890.30793214786</v>
+        <v>45890.30793215278</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>23/08 19:30</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>2.95</t>
-        </is>
+      <c r="F40" t="n">
+        <v>2.95</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45890.30793214786</v>
+        <v>45890.30793215278</v>
       </c>
     </row>
     <row r="41">
@@ -2186,10 +2182,8 @@
           <t>23/08 17:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
+      <c r="F41" t="n">
+        <v>2.85</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2202,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45890.30793214786</v>
+        <v>45890.30793215278</v>
       </c>
     </row>
     <row r="42">
@@ -2231,10 +2225,8 @@
           <t>23/08 14:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F42" t="n">
+        <v>2.9</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2247,7 +2239,142 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45890.30793214786</v>
+        <v>45890.30793215278</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 22.5 - tirs | FC St. Pau</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>FC St. Pauli – Borussia DortmundAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Moins que 22.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>23/08 16:30</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+17,3%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45890.35358429811</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 13.5 - tirs1re équipe | Anderlecht</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Anderlecht – AEK AthènesLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>42,0%</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>+15,5%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>45890.35358429811</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.51re équipe | Qingdao Ha</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Qingdao Hainiu FC – Shanghai ShenhuaSuper League</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>23/08 11:35</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2,21%</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>45890.35358429811</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2268,10 +2268,8 @@
           <t>23/08 16:30</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F43" t="n">
+        <v>3.3</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2284,7 +2282,7 @@
         </is>
       </c>
       <c r="I43" s="2" t="n">
-        <v>45890.35358429811</v>
+        <v>45890.35358429398</v>
       </c>
     </row>
     <row r="44">
@@ -2313,10 +2311,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F44" t="n">
+        <v>2.75</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2329,7 +2325,7 @@
         </is>
       </c>
       <c r="I44" s="2" t="n">
-        <v>45890.35358429811</v>
+        <v>45890.35358429398</v>
       </c>
     </row>
     <row r="45">
@@ -2358,10 +2354,8 @@
           <t>23/08 11:35</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F45" t="n">
+        <v>50</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2374,7 +2368,52 @@
         </is>
       </c>
       <c r="I45" s="2" t="n">
-        <v>45890.35358429811</v>
+        <v>45890.35358429398</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis | 1 - aces | H.Medjedov</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>ParionsSport(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>H.Medjedovic – G.MpetshiATP - Winston Salem</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1 - aces</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>21/08 22:30</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>25,1%</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>+25,3%</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>45890.39166790622</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2397,10 +2397,8 @@
           <t>21/08 22:30</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F46" t="n">
+        <v>5</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2413,7 +2411,232 @@
         </is>
       </c>
       <c r="I46" s="2" t="n">
-        <v>45890.39166790622</v>
+        <v>45890.39166790509</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Panathinai</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Panathinaikos – SamsunsporLigue Europa</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>+33,6%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>45890.43280324157</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 27.5 - tirs | Bayern Mun</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Bayern Munich – RB LeipzigBundesliga</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Moins que 27.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>50,3%</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>+25,7%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>45890.43280324157</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 24.5 - tirs | FC Heidenh</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>FC Heidenheim 1846 – WolfsbourgBundesliga</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>23/08 13:30</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>45,5%</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>+20,5%</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>45890.43280324157</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Universita</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Universitatea Craiova – FC Petrolul PloiestiLiga 1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>24/08 15:30</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>+17,7%</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>45890.43280324157</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 12.5 - tirs1re équipe | Slovan Bra</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Slovan Bratislava – Young BoysEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Moins que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>21/08 18:15</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45890.43280324157</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2440,10 +2440,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F47" t="n">
+        <v>60</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2456,7 +2454,7 @@
         </is>
       </c>
       <c r="I47" s="2" t="n">
-        <v>45890.43280324157</v>
+        <v>45890.43280324074</v>
       </c>
     </row>
     <row r="48">
@@ -2485,10 +2483,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="F48" t="n">
+        <v>2.5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2501,7 +2497,7 @@
         </is>
       </c>
       <c r="I48" s="2" t="n">
-        <v>45890.43280324157</v>
+        <v>45890.43280324074</v>
       </c>
     </row>
     <row r="49">
@@ -2530,10 +2526,8 @@
           <t>23/08 13:30</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2.65</t>
-        </is>
+      <c r="F49" t="n">
+        <v>2.65</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2546,7 +2540,7 @@
         </is>
       </c>
       <c r="I49" s="2" t="n">
-        <v>45890.43280324157</v>
+        <v>45890.43280324074</v>
       </c>
     </row>
     <row r="50">
@@ -2575,10 +2569,8 @@
           <t>24/08 15:30</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F50" t="n">
+        <v>55</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2591,7 +2583,7 @@
         </is>
       </c>
       <c r="I50" s="2" t="n">
-        <v>45890.43280324157</v>
+        <v>45890.43280324074</v>
       </c>
     </row>
     <row r="51">
@@ -2620,23 +2612,246 @@
           <t>21/08 18:15</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>39,6%</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>+14,9%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>45890.43280324074</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 15.5 - tirs1re équipe | FC Midtjyl</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FC Midtjylland – Kuopio PSEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Moins que 15.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>21/08 16:30</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>53,4%</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>+21,8%</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>45890.47163659257</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 12.5 - tirs2e équipe | Atletico L</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Atletico Lanus – Central CórdobaInternational - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>22/08 00:30</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>35,8%</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>+18,1%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>45890.47163659257</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 19.5 - tirs1re équipe | Arsenal – </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Arsenal – LeedsAngleterre - Angl. Premier League</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Plus que 19.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>23/08 16:30</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
         <is>
           <t>2.90</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>39,6%</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>+14,9%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>45890.43280324157</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>38,6%</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>+12,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>45890.47163659257</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football | 11-2- se qualifie | Levski Sof</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Winamax(FR)Football</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Levski Sofia – AZ AlkmaarEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>22,4%</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>+11,7%</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>45890.47163659257</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 10.5 - tirs2e équipe | Maccabi Te</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Maccabi Tel-Aviv – Dynamo KievEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Moins que 10.5 - tirs2e équipe</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>47,3%</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>+11,2%</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>45890.47163659257</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2655,10 +2655,8 @@
           <t>21/08 16:30</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2.28</t>
-        </is>
+      <c r="F52" t="n">
+        <v>2.28</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2671,7 +2669,7 @@
         </is>
       </c>
       <c r="I52" s="2" t="n">
-        <v>45890.47163659257</v>
+        <v>45890.47163659722</v>
       </c>
     </row>
     <row r="53">
@@ -2700,10 +2698,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
+      <c r="F53" t="n">
+        <v>3.3</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2716,7 +2712,7 @@
         </is>
       </c>
       <c r="I53" s="2" t="n">
-        <v>45890.47163659257</v>
+        <v>45890.47163659722</v>
       </c>
     </row>
     <row r="54">
@@ -2745,10 +2741,8 @@
           <t>23/08 16:30</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F54" t="n">
+        <v>2.9</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2761,7 +2755,7 @@
         </is>
       </c>
       <c r="I54" s="2" t="n">
-        <v>45890.47163659257</v>
+        <v>45890.47163659722</v>
       </c>
     </row>
     <row r="55">
@@ -2790,10 +2784,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="F55" t="n">
+        <v>5</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2806,7 +2798,7 @@
         </is>
       </c>
       <c r="I55" s="2" t="n">
-        <v>45890.47163659257</v>
+        <v>45890.47163659722</v>
       </c>
     </row>
     <row r="56">
@@ -2835,10 +2827,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="F56" t="n">
+        <v>2.35</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2851,7 +2841,142 @@
         </is>
       </c>
       <c r="I56" s="2" t="n">
-        <v>45890.47163659257</v>
+        <v>45890.47163659722</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré1re équipe | Zrinjski M</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Zrinjski Mostar – UtrechtEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>+10,5%</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>45890.53032620125</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 25.5 - tirs | Bayern Mun</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Bayern Munich – RB LeipzigAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Moins que 25.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>22/08 18:30</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>35,6%</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>45890.53032620125</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 11-2- se qualifie | Levski Sof</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Levski Sofia – AZ AlkmaarEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>11-2- se qualifie</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>4.80</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>22,9%</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>+9,82%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>45890.53032620125</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I59"/>
+  <dimension ref="A1:I65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2870,10 +2870,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F57" t="n">
+        <v>3</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2886,7 +2884,7 @@
         </is>
       </c>
       <c r="I57" s="2" t="n">
-        <v>45890.53032620125</v>
+        <v>45890.53032620371</v>
       </c>
     </row>
     <row r="58">
@@ -2915,10 +2913,8 @@
           <t>22/08 18:30</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="F58" t="n">
+        <v>3.1</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2931,7 +2927,7 @@
         </is>
       </c>
       <c r="I58" s="2" t="n">
-        <v>45890.53032620125</v>
+        <v>45890.53032620371</v>
       </c>
     </row>
     <row r="59">
@@ -2960,10 +2956,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>4.80</t>
-        </is>
+      <c r="F59" t="n">
+        <v>4.8</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2976,7 +2970,277 @@
         </is>
       </c>
       <c r="I59" s="2" t="n">
-        <v>45890.53032620125</v>
+        <v>45890.53032620371</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football | 2 | Breidablik</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>PMU(FR)Football</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Breidablik – SS VirtusEurope. Europa Conférence (Q)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2,50%</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>+37,4%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>45890.56390981723</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Moins que 9.5 - tirs1re équipe | FC St. Pau</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FC St. Pauli – DortmundBundesliga</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Moins que 9.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>23/08 16:30</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>+23,7%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>45890.56390981723</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 7.5 - tir cadré | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Lech Poznan – GenkEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Moins que 7.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>21/08 18:30</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>33,1%</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>+15,7%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>45890.56390981723</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 18.5 - tirs1re équipe | Arsenal – </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Arsenal – Leeds UnitedPremier League</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Plus que 18.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>23/08 16:30</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>+14,0%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>45890.56390981723</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 3.5 - tir cadré1re équipe | Shkendija </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Shkendija Tetovo – Ludogorets Razgrad385076e7 Europe - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>59,9%</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>+10,8%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>45890.56390981723</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 12.5 - tirs1re équipe | Maccabi Te</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Maccabi Tel-Aviv – Dynamo KievEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Plus que 12.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>56,8%</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>+10,3%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>45890.56390981723</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:I69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2999,10 +2999,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F60" t="n">
+        <v>55</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -3015,7 +3013,7 @@
         </is>
       </c>
       <c r="I60" s="2" t="n">
-        <v>45890.56390981723</v>
+        <v>45890.56390981482</v>
       </c>
     </row>
     <row r="61">
@@ -3044,10 +3042,8 @@
           <t>23/08 16:30</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F61" t="n">
+        <v>2.7</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -3060,7 +3056,7 @@
         </is>
       </c>
       <c r="I61" s="2" t="n">
-        <v>45890.56390981723</v>
+        <v>45890.56390981482</v>
       </c>
     </row>
     <row r="62">
@@ -3089,10 +3085,8 @@
           <t>21/08 18:30</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F62" t="n">
+        <v>3.5</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -3105,7 +3099,7 @@
         </is>
       </c>
       <c r="I62" s="2" t="n">
-        <v>45890.56390981723</v>
+        <v>45890.56390981482</v>
       </c>
     </row>
     <row r="63">
@@ -3134,10 +3128,8 @@
           <t>23/08 16:30</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F63" t="n">
+        <v>2.7</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -3150,7 +3142,7 @@
         </is>
       </c>
       <c r="I63" s="2" t="n">
-        <v>45890.56390981723</v>
+        <v>45890.56390981482</v>
       </c>
     </row>
     <row r="64">
@@ -3179,10 +3171,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="F64" t="n">
+        <v>1.85</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3195,7 +3185,7 @@
         </is>
       </c>
       <c r="I64" s="2" t="n">
-        <v>45890.56390981723</v>
+        <v>45890.56390981482</v>
       </c>
     </row>
     <row r="65">
@@ -3224,10 +3214,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
+      <c r="F65" t="n">
+        <v>1.94</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3240,7 +3228,187 @@
         </is>
       </c>
       <c r="I65" s="2" t="n">
-        <v>45890.56390981723</v>
+        <v>45890.56390981482</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Plus que 5.5 - tir cadré2e équipe | Hibernian </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Hibernian – Legia VarsovieEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Plus que 5.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>26,5%</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>+19,4%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>45890.59892245251</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Moins que 24.5 - tirs | Eintracht </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Eintracht Francfort – Werder BrêmeBundesliga</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Moins que 24.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>23/08 13:30</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>39,1%</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>+17,2%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>45890.59892245251</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 9.5 - tir cadré | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Arda KardzhaliLigue Europa Conférence</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Plus que 9.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>31,0%</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>+8,36%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>45890.59892245251</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Aris Thess</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Aris Thessalonique – VolosSuper League</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>23/08 17:00</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2,16%</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>+8,11%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>45890.59892245251</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:I73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3257,10 +3257,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
+      <c r="F66" t="n">
+        <v>4.5</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3273,7 +3271,7 @@
         </is>
       </c>
       <c r="I66" s="2" t="n">
-        <v>45890.59892245251</v>
+        <v>45890.5989224537</v>
       </c>
     </row>
     <row r="67">
@@ -3302,10 +3300,8 @@
           <t>23/08 13:30</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F67" t="n">
+        <v>3</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3318,7 +3314,7 @@
         </is>
       </c>
       <c r="I67" s="2" t="n">
-        <v>45890.59892245251</v>
+        <v>45890.5989224537</v>
       </c>
     </row>
     <row r="68">
@@ -3347,10 +3343,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
+      <c r="F68" t="n">
+        <v>3.5</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3363,7 +3357,7 @@
         </is>
       </c>
       <c r="I68" s="2" t="n">
-        <v>45890.59892245251</v>
+        <v>45890.5989224537</v>
       </c>
     </row>
     <row r="69">
@@ -3392,10 +3386,8 @@
           <t>23/08 17:00</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F69" t="n">
+        <v>50</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3408,7 +3400,187 @@
         </is>
       </c>
       <c r="I69" s="2" t="n">
-        <v>45890.59892245251</v>
+        <v>45890.5989224537</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football | Plus que 6.5 | FH Hafnarf</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Bwin(FR)Football</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>FH Hafnarfjördur – IB VestmannaeyjaIslande - Urvalsdeild</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Plus que 6.5</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>24/08 18:00</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>10.50</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>17,7%</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>+85,5%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>45890.64156483065</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.51re équipe | NAC Breda </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>NAC Breda – AZ AlkmaarEredivisie</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Plus que 3.51re équipe</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>31/08 14:45</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>55.00</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>+12,3%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>45890.64156483065</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 6.5 - tir cadré | Heidenheim</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Heidenheim – WolfsburgAllemagne - Allemagne Bundesliga</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Moins que 6.5 - tir cadré</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>23/08 13:30</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>26,0%</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>+10,4%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>45890.64156483065</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Football | Moins que 3.5 - tir cadré1re équipe | Hibernian </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Hibernian – Legia VarsovieEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - tir cadré1re équipe</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>37,8%</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>+9,59%</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>45890.64156483065</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I73"/>
+  <dimension ref="A1:I75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3429,10 +3429,8 @@
           <t>24/08 18:00</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>10.50</t>
-        </is>
+      <c r="F70" t="n">
+        <v>10.5</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3445,7 +3443,7 @@
         </is>
       </c>
       <c r="I70" s="2" t="n">
-        <v>45890.64156483065</v>
+        <v>45890.64156482639</v>
       </c>
     </row>
     <row r="71">
@@ -3474,10 +3472,8 @@
           <t>31/08 14:45</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>55.00</t>
-        </is>
+      <c r="F71" t="n">
+        <v>55</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3490,7 +3486,7 @@
         </is>
       </c>
       <c r="I71" s="2" t="n">
-        <v>45890.64156483065</v>
+        <v>45890.64156482639</v>
       </c>
     </row>
     <row r="72">
@@ -3519,10 +3515,8 @@
           <t>23/08 13:30</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F72" t="n">
+        <v>4.25</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3535,7 +3529,7 @@
         </is>
       </c>
       <c r="I72" s="2" t="n">
-        <v>45890.64156483065</v>
+        <v>45890.64156482639</v>
       </c>
     </row>
     <row r="73">
@@ -3564,10 +3558,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
+      <c r="F73" t="n">
+        <v>2.9</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3580,7 +3572,97 @@
         </is>
       </c>
       <c r="I73" s="2" t="n">
-        <v>45890.64156483065</v>
+        <v>45890.64156482639</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 3.5 - tir cadré2e équipe | Rakow Czes</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Rakow Czestochowa – Arda FKEurope - Ligue Conférence</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Plus que 3.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>34,7%</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>+30,1%</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>45890.68898428178</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 13.5 - tirs1re équipe | Lech Pozna</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Lech Poznan – GenkEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Plus que 13.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>21/08 18:30</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>+12,5%</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>45890.68898428178</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I75"/>
+  <dimension ref="A1:I77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3601,10 +3601,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
+      <c r="F74" t="n">
+        <v>3.75</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3617,7 +3615,7 @@
         </is>
       </c>
       <c r="I74" s="2" t="n">
-        <v>45890.68898428178</v>
+        <v>45890.68898428241</v>
       </c>
     </row>
     <row r="75">
@@ -3646,10 +3644,8 @@
           <t>21/08 18:30</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
+      <c r="F75" t="n">
+        <v>3</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3662,7 +3658,97 @@
         </is>
       </c>
       <c r="I75" s="2" t="n">
-        <v>45890.68898428178</v>
+        <v>45890.68898428241</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 2.51re équipe | Lincoln Re</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Lincoln Red Imps FC – Sporting BragaLigue Europa</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>21/08 19:00</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>50.00</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>+12,3%</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>45890.72875089975</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 8.5 - tirs1re équipe | Zrinjski M</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Zrinjski Mostar – UtrechtEurope - Ligue Europa</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Moins que 8.5 - tirs1re équipe</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>21/08 18:00</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>40,0%</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>+10,0%</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>45890.72875089975</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I77"/>
+  <dimension ref="A1:I79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3687,10 +3687,8 @@
           <t>21/08 19:00</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>50.00</t>
-        </is>
+      <c r="F76" t="n">
+        <v>50</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3703,7 +3701,7 @@
         </is>
       </c>
       <c r="I76" s="2" t="n">
-        <v>45890.72875089975</v>
+        <v>45890.72875090278</v>
       </c>
     </row>
     <row r="77">
@@ -3732,10 +3730,8 @@
           <t>21/08 18:00</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
+      <c r="F77" t="n">
+        <v>2.75</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3748,7 +3744,97 @@
         </is>
       </c>
       <c r="I77" s="2" t="n">
-        <v>45890.72875089975</v>
+        <v>45890.72875090278</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 4.5 - tir cadré2e équipe | River Plat</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>River Plate – Libertad AsuncionInternational - Copa Libertadores</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Plus que 4.5 - tir cadré2e équipe</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>22/08 00:30</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>34,2%</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>+45,5%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>45890.77115587485</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Llaneros F</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Llaneros FC – AD PastoPrimera A</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>23/08 01:10</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>45.00</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2,44%</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>+9,80%</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>45890.77115587485</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I79"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3773,10 +3773,8 @@
           <t>22/08 00:30</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>4.25</t>
-        </is>
+      <c r="F78" t="n">
+        <v>4.25</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3789,7 +3787,7 @@
         </is>
       </c>
       <c r="I78" s="2" t="n">
-        <v>45890.77115587485</v>
+        <v>45890.77115587963</v>
       </c>
     </row>
     <row r="79">
@@ -3818,10 +3816,8 @@
           <t>23/08 01:10</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>45.00</t>
-        </is>
+      <c r="F79" t="n">
+        <v>45</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3834,7 +3830,52 @@
         </is>
       </c>
       <c r="I79" s="2" t="n">
-        <v>45890.77115587485</v>
+        <v>45890.77115587963</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Moins que 26.5 - tirs | Godoy Cruz</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Godoy Cruz – Atletico Mineiro385076e7 International - Copa Sudamericana</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Moins que 26.5 - tirs</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>21/08 22:00</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>40,6%</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>+9,71%</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>45890.80378356082</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I80"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3859,10 +3859,8 @@
           <t>21/08 22:00</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="F80" t="n">
+        <v>2.7</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3875,7 +3873,97 @@
         </is>
       </c>
       <c r="I80" s="2" t="n">
-        <v>45890.80378356082</v>
+        <v>45890.80378356481</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unibet(FR)Football | Plus que 3.52e équipe | Leganes – </t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Leganes – CadixLaLiga2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>22/08 19:30</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>60.00</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>+37,4%</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>45890.85000002521</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis | Moins que 3.5 - break2e participant | Alycia Par</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Tennis</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Alycia Parks – Rebecca SramkovaWTA 500 Monterrey</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Moins que 3.5 - break2e participant</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>21/08 23:00</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>52,3%</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>+7,11%</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>45890.85000002521</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-08-21.xlsx
+++ b/data/valuebets_database_2025-08-21.xlsx
@@ -3902,10 +3902,8 @@
           <t>22/08 19:30</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>60.00</t>
-        </is>
+      <c r="F81" t="n">
+        <v>60</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3918,7 +3916,7 @@
         </is>
       </c>
       <c r="I81" s="2" t="n">
-        <v>45890.85000002521</v>
+        <v>45890.85000002315</v>
       </c>
     </row>
     <row r="82">
@@ -3947,10 +3945,8 @@
           <t>21/08 23:00</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
+      <c r="F82" t="n">
+        <v>2.05</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3963,7 +3959,7 @@
         </is>
       </c>
       <c r="I82" s="2" t="n">
-        <v>45890.85000002521</v>
+        <v>45890.85000002315</v>
       </c>
     </row>
   </sheetData>
